--- a/test/s2t/s2t_30_csv_csv_3mill50cols.xlsx
+++ b/test/s2t/s2t_30_csv_csv_3mill50cols.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My_Workspaces\GitHub\QE_ATF\test\s2t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2450C0-7DE5-42E3-854A-435A86279EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1608661E-04E9-41B8-BE53-DCCD7F0E7B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{60D25328-0517-4E51-B966-9D3337769260}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{60D25328-0517-4E51-B966-9D3337769260}"/>
   </bookViews>
   <sheets>
     <sheet name="MappingConfiguration" sheetId="1" r:id="rId1"/>
@@ -317,12 +317,6 @@
     <t>,</t>
   </si>
   <si>
-    <t>/app/test/data/source</t>
-  </si>
-  <si>
-    <t>/app/test/data/target</t>
-  </si>
-  <si>
     <t>ArgentinaPropertiesTgt</t>
   </si>
   <si>
@@ -495,6 +489,12 @@
   </si>
   <si>
     <t>lockin_period</t>
+  </si>
+  <si>
+    <t>test/data/source</t>
+  </si>
+  <si>
+    <t>test/data/target</t>
   </si>
 </sst>
 </file>
@@ -980,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1018,7 +1018,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1060,7 +1060,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1096,7 +1096,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1104,7 +1104,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1146,7 +1146,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1188,7 +1188,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1196,7 +1196,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1401,7 +1401,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D3" s="6">
         <v>2</v>
@@ -1421,13 +1421,13 @@
         <v>65</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" s="6">
         <v>3</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>67</v>
@@ -1441,13 +1441,13 @@
         <v>65</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" s="6">
         <v>4</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>67</v>
@@ -1461,13 +1461,13 @@
         <v>65</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D6" s="6">
         <v>5</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>67</v>
@@ -1481,13 +1481,13 @@
         <v>65</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" s="6">
         <v>6</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>67</v>
@@ -1501,13 +1501,13 @@
         <v>65</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D8" s="6">
         <v>7</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>67</v>
@@ -1521,7 +1521,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D9" s="6">
         <v>8</v>
@@ -1541,7 +1541,7 @@
         <v>65</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D10" s="6">
         <v>9</v>
@@ -1561,7 +1561,7 @@
         <v>65</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D11" s="6">
         <v>10</v>
@@ -1581,7 +1581,7 @@
         <v>65</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D12" s="6">
         <v>11</v>
@@ -1601,7 +1601,7 @@
         <v>65</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D13" s="6">
         <v>12</v>
@@ -1621,7 +1621,7 @@
         <v>65</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D14" s="6">
         <v>13</v>
@@ -1641,13 +1641,13 @@
         <v>65</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D15" s="6">
         <v>14</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>67</v>
@@ -1661,13 +1661,13 @@
         <v>65</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D16" s="6">
         <v>15</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>67</v>
@@ -1681,13 +1681,13 @@
         <v>65</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D17" s="6">
         <v>16</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>67</v>
@@ -1701,13 +1701,13 @@
         <v>65</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D18" s="6">
         <v>17</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>67</v>
@@ -1721,13 +1721,13 @@
         <v>65</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19" s="6">
         <v>18</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>67</v>
@@ -1741,13 +1741,13 @@
         <v>65</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D20" s="6">
         <v>19</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>67</v>
@@ -1761,7 +1761,7 @@
         <v>65</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D21" s="6">
         <v>20</v>
@@ -1781,7 +1781,7 @@
         <v>65</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D22" s="6">
         <v>21</v>
@@ -1801,7 +1801,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D23" s="6">
         <v>22</v>
@@ -1821,7 +1821,7 @@
         <v>65</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D24" s="6">
         <v>23</v>
@@ -1841,7 +1841,7 @@
         <v>65</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D25" s="6">
         <v>24</v>
@@ -1861,7 +1861,7 @@
         <v>65</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6">
         <v>25</v>
@@ -1881,13 +1881,13 @@
         <v>65</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D27" s="6">
         <v>26</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>67</v>
@@ -1901,13 +1901,13 @@
         <v>65</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D28" s="6">
         <v>27</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>67</v>
@@ -1921,13 +1921,13 @@
         <v>65</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D29" s="6">
         <v>28</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>67</v>
@@ -1941,13 +1941,13 @@
         <v>65</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D30" s="6">
         <v>29</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>67</v>
@@ -1961,13 +1961,13 @@
         <v>65</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D31" s="6">
         <v>30</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>67</v>
@@ -1981,7 +1981,7 @@
         <v>65</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D32" s="6">
         <v>31</v>
@@ -2001,7 +2001,7 @@
         <v>65</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D33" s="6">
         <v>32</v>
@@ -2021,7 +2021,7 @@
         <v>65</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D34" s="6">
         <v>33</v>
@@ -2041,7 +2041,7 @@
         <v>65</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D35" s="6">
         <v>34</v>
@@ -2061,7 +2061,7 @@
         <v>65</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" s="6">
         <v>35</v>
@@ -2081,13 +2081,13 @@
         <v>65</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D37" s="6">
         <v>36</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>67</v>
@@ -2101,13 +2101,13 @@
         <v>65</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D38" s="6">
         <v>37</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>67</v>
@@ -2121,13 +2121,13 @@
         <v>65</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D39" s="6">
         <v>38</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>67</v>
@@ -2141,13 +2141,13 @@
         <v>65</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D40" s="6">
         <v>39</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>67</v>
@@ -2161,13 +2161,13 @@
         <v>65</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D41" s="6">
         <v>40</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>67</v>
@@ -2181,7 +2181,7 @@
         <v>65</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D42" s="6">
         <v>41</v>
@@ -2201,7 +2201,7 @@
         <v>65</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D43" s="6">
         <v>42</v>
@@ -2221,7 +2221,7 @@
         <v>65</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D44" s="6">
         <v>43</v>
@@ -2241,7 +2241,7 @@
         <v>65</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D45" s="6">
         <v>44</v>
@@ -2261,7 +2261,7 @@
         <v>65</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D46" s="6">
         <v>45</v>
@@ -2281,13 +2281,13 @@
         <v>65</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D47" s="6">
         <v>46</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>67</v>
@@ -2301,7 +2301,7 @@
         <v>65</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D48" s="6">
         <v>47</v>
@@ -2321,13 +2321,13 @@
         <v>65</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D49" s="6">
         <v>48</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>67</v>
@@ -2341,7 +2341,7 @@
         <v>65</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D50" s="6">
         <v>49</v>
@@ -2361,7 +2361,7 @@
         <v>65</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D51" s="6">
         <v>50</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>68</v>
@@ -2392,13 +2392,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D53" s="6">
         <v>2</v>
@@ -2412,19 +2412,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D54" s="6">
         <v>3</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>67</v>
@@ -2432,19 +2432,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D55" s="6">
         <v>4</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>67</v>
@@ -2452,19 +2452,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D56" s="6">
         <v>5</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>67</v>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D57" s="6">
         <v>6</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>67</v>
@@ -2492,19 +2492,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D58" s="6">
         <v>7</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>67</v>
@@ -2512,13 +2512,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D59" s="6">
         <v>8</v>
@@ -2532,13 +2532,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D60" s="6">
         <v>9</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D61" s="6">
         <v>10</v>
@@ -2572,13 +2572,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D62" s="6">
         <v>11</v>
@@ -2592,13 +2592,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D63" s="6">
         <v>12</v>
@@ -2612,13 +2612,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D64" s="6">
         <v>13</v>
@@ -2632,19 +2632,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D65" s="6">
         <v>14</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>67</v>
@@ -2652,19 +2652,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D66" s="6">
         <v>15</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>67</v>
@@ -2672,19 +2672,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D67" s="6">
         <v>16</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>67</v>
@@ -2692,19 +2692,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D68" s="6">
         <v>17</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>67</v>
@@ -2712,19 +2712,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D69" s="6">
         <v>18</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>67</v>
@@ -2732,19 +2732,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D70" s="6">
         <v>19</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>67</v>
@@ -2752,13 +2752,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D71" s="6">
         <v>20</v>
@@ -2772,13 +2772,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D72" s="6">
         <v>21</v>
@@ -2792,13 +2792,13 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D73" s="6">
         <v>22</v>
@@ -2812,13 +2812,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D74" s="6">
         <v>23</v>
@@ -2832,13 +2832,13 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D75" s="6">
         <v>24</v>
@@ -2852,13 +2852,13 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D76" s="6">
         <v>25</v>
@@ -2872,19 +2872,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B77" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="D77" s="6">
         <v>26</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>67</v>
@@ -2892,19 +2892,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D78" s="6">
         <v>27</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>67</v>
@@ -2912,19 +2912,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D79" s="6">
         <v>28</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>67</v>
@@ -2932,19 +2932,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D80" s="6">
         <v>29</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>67</v>
@@ -2952,19 +2952,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D81" s="6">
         <v>30</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>67</v>
@@ -2972,13 +2972,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D82" s="6">
         <v>31</v>
@@ -2992,13 +2992,13 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D83" s="6">
         <v>32</v>
@@ -3012,13 +3012,13 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D84" s="6">
         <v>33</v>
@@ -3032,13 +3032,13 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D85" s="6">
         <v>34</v>
@@ -3052,13 +3052,13 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D86" s="6">
         <v>35</v>
@@ -3072,19 +3072,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D87" s="6">
         <v>36</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>67</v>
@@ -3092,19 +3092,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D88" s="6">
         <v>37</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>67</v>
@@ -3112,19 +3112,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D89" s="6">
         <v>38</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>67</v>
@@ -3132,19 +3132,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D90" s="6">
         <v>39</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>67</v>
@@ -3152,19 +3152,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D91" s="6">
         <v>40</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>67</v>
@@ -3172,13 +3172,13 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D92" s="6">
         <v>41</v>
@@ -3192,13 +3192,13 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D93" s="6">
         <v>42</v>
@@ -3212,13 +3212,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D94" s="6">
         <v>43</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D95" s="6">
         <v>44</v>
@@ -3252,13 +3252,13 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D96" s="6">
         <v>45</v>
@@ -3272,19 +3272,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D97" s="6">
         <v>46</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>67</v>
@@ -3292,13 +3292,13 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D98" s="6">
         <v>47</v>
@@ -3312,19 +3312,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D99" s="6">
         <v>48</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>67</v>
@@ -3332,13 +3332,13 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D100" s="6">
         <v>49</v>
@@ -3352,13 +3352,13 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D101" s="6">
         <v>50</v>
@@ -3395,7 +3395,7 @@
         <v>87</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D103" s="6">
         <v>2</v>
@@ -3415,13 +3415,13 @@
         <v>87</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D104" s="6">
         <v>3</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>67</v>
@@ -3435,13 +3435,13 @@
         <v>87</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D105" s="6">
         <v>4</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>67</v>
@@ -3455,13 +3455,13 @@
         <v>87</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D106" s="6">
         <v>5</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>67</v>
@@ -3475,13 +3475,13 @@
         <v>87</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D107" s="6">
         <v>6</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>67</v>
@@ -3495,13 +3495,13 @@
         <v>87</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D108" s="6">
         <v>7</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>67</v>
@@ -3515,7 +3515,7 @@
         <v>87</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D109" s="6">
         <v>8</v>
@@ -3535,7 +3535,7 @@
         <v>87</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D110" s="6">
         <v>9</v>
@@ -3555,7 +3555,7 @@
         <v>87</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D111" s="6">
         <v>10</v>
@@ -3575,7 +3575,7 @@
         <v>87</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D112" s="6">
         <v>11</v>
@@ -3595,7 +3595,7 @@
         <v>87</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D113" s="6">
         <v>12</v>
@@ -3615,7 +3615,7 @@
         <v>87</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D114" s="6">
         <v>13</v>
@@ -3635,13 +3635,13 @@
         <v>87</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D115" s="6">
         <v>14</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>67</v>
@@ -3655,13 +3655,13 @@
         <v>87</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D116" s="6">
         <v>15</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>67</v>
@@ -3675,13 +3675,13 @@
         <v>87</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D117" s="6">
         <v>16</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>67</v>
@@ -3695,13 +3695,13 @@
         <v>87</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D118" s="6">
         <v>17</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>67</v>
@@ -3715,13 +3715,13 @@
         <v>87</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D119" s="6">
         <v>18</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>67</v>
@@ -3735,13 +3735,13 @@
         <v>87</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D120" s="6">
         <v>19</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>67</v>
@@ -3755,7 +3755,7 @@
         <v>87</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D121" s="6">
         <v>20</v>
@@ -3775,7 +3775,7 @@
         <v>87</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D122" s="6">
         <v>21</v>
@@ -3795,7 +3795,7 @@
         <v>87</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D123" s="6">
         <v>22</v>
@@ -3815,7 +3815,7 @@
         <v>87</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D124" s="6">
         <v>23</v>
@@ -3835,7 +3835,7 @@
         <v>87</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D125" s="6">
         <v>24</v>
@@ -3855,7 +3855,7 @@
         <v>87</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D126" s="6">
         <v>25</v>
@@ -3875,13 +3875,13 @@
         <v>87</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D127" s="6">
         <v>26</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>67</v>
@@ -3895,13 +3895,13 @@
         <v>87</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D128" s="6">
         <v>27</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>67</v>
@@ -3915,13 +3915,13 @@
         <v>87</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D129" s="6">
         <v>28</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>67</v>
@@ -3935,13 +3935,13 @@
         <v>87</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D130" s="6">
         <v>29</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>67</v>
@@ -3955,13 +3955,13 @@
         <v>87</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D131" s="6">
         <v>30</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>67</v>
@@ -3975,7 +3975,7 @@
         <v>87</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D132" s="6">
         <v>31</v>
@@ -3995,7 +3995,7 @@
         <v>87</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D133" s="6">
         <v>32</v>
@@ -4015,7 +4015,7 @@
         <v>87</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D134" s="6">
         <v>33</v>
@@ -4035,7 +4035,7 @@
         <v>87</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D135" s="6">
         <v>34</v>
@@ -4055,7 +4055,7 @@
         <v>87</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D136" s="6">
         <v>35</v>
@@ -4075,13 +4075,13 @@
         <v>87</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D137" s="6">
         <v>36</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>67</v>
@@ -4095,13 +4095,13 @@
         <v>87</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D138" s="6">
         <v>37</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>67</v>
@@ -4115,13 +4115,13 @@
         <v>87</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D139" s="6">
         <v>38</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>67</v>
@@ -4135,13 +4135,13 @@
         <v>87</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D140" s="6">
         <v>39</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>67</v>
@@ -4155,13 +4155,13 @@
         <v>87</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D141" s="6">
         <v>40</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>67</v>
@@ -4175,7 +4175,7 @@
         <v>87</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D142" s="6">
         <v>41</v>
@@ -4195,7 +4195,7 @@
         <v>87</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D143" s="6">
         <v>42</v>
@@ -4215,7 +4215,7 @@
         <v>87</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D144" s="6">
         <v>43</v>
@@ -4235,7 +4235,7 @@
         <v>87</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D145" s="6">
         <v>44</v>
@@ -4255,7 +4255,7 @@
         <v>87</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D146" s="6">
         <v>45</v>
@@ -4275,13 +4275,13 @@
         <v>87</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D147" s="6">
         <v>46</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>67</v>
@@ -4295,7 +4295,7 @@
         <v>87</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D148" s="6">
         <v>47</v>
@@ -4315,13 +4315,13 @@
         <v>87</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D149" s="6">
         <v>48</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>67</v>
@@ -4335,7 +4335,7 @@
         <v>87</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D150" s="6">
         <v>49</v>
@@ -4355,7 +4355,7 @@
         <v>87</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D151" s="6">
         <v>50</v>
@@ -4453,10 +4453,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>68</v>
@@ -4485,13 +4485,13 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>64</v>
@@ -4500,7 +4500,7 @@
         <v>65</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>82</v>
@@ -4517,13 +4517,13 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>64</v>
@@ -4532,7 +4532,7 @@
         <v>65</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>82</v>
@@ -4549,13 +4549,13 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>64</v>
@@ -4564,7 +4564,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>82</v>
@@ -4581,13 +4581,13 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>64</v>
@@ -4596,7 +4596,7 @@
         <v>65</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>82</v>
@@ -4613,13 +4613,13 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>64</v>
@@ -4628,7 +4628,7 @@
         <v>65</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>82</v>
@@ -4645,13 +4645,13 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>64</v>
@@ -4660,7 +4660,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>82</v>
@@ -4677,13 +4677,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>64</v>
@@ -4692,7 +4692,7 @@
         <v>65</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>82</v>
@@ -4709,13 +4709,13 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>64</v>
@@ -4724,7 +4724,7 @@
         <v>65</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>82</v>
@@ -4741,13 +4741,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>64</v>
@@ -4756,7 +4756,7 @@
         <v>65</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>82</v>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>64</v>
@@ -4788,7 +4788,7 @@
         <v>65</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>82</v>
@@ -4805,13 +4805,13 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>64</v>
@@ -4820,7 +4820,7 @@
         <v>65</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>82</v>
@@ -4837,13 +4837,13 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>64</v>
@@ -4852,7 +4852,7 @@
         <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>82</v>
@@ -4869,13 +4869,13 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>64</v>
@@ -4884,7 +4884,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>82</v>
@@ -4901,13 +4901,13 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>64</v>
@@ -4916,7 +4916,7 @@
         <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>82</v>
@@ -4933,13 +4933,13 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>64</v>
@@ -4948,7 +4948,7 @@
         <v>65</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>82</v>
@@ -4965,13 +4965,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>64</v>
@@ -4980,7 +4980,7 @@
         <v>65</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>82</v>
@@ -4997,13 +4997,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>64</v>
@@ -5012,7 +5012,7 @@
         <v>65</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>82</v>
@@ -5029,13 +5029,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>64</v>
@@ -5044,7 +5044,7 @@
         <v>65</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>82</v>
@@ -5061,13 +5061,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>64</v>
@@ -5076,7 +5076,7 @@
         <v>65</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>82</v>
@@ -5093,13 +5093,13 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>64</v>
@@ -5108,7 +5108,7 @@
         <v>65</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>82</v>
@@ -5125,13 +5125,13 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>64</v>
@@ -5140,7 +5140,7 @@
         <v>65</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>82</v>
@@ -5157,13 +5157,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>64</v>
@@ -5172,7 +5172,7 @@
         <v>65</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>82</v>
@@ -5189,13 +5189,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>64</v>
@@ -5204,7 +5204,7 @@
         <v>65</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>82</v>
@@ -5221,13 +5221,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>64</v>
@@ -5236,7 +5236,7 @@
         <v>65</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>82</v>
@@ -5253,14 +5253,14 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>127</v>
-      </c>
       <c r="D27" s="6" t="s">
         <v>64</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>65</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>82</v>
@@ -5285,13 +5285,13 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>64</v>
@@ -5300,7 +5300,7 @@
         <v>65</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>82</v>
@@ -5317,13 +5317,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>64</v>
@@ -5332,7 +5332,7 @@
         <v>65</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>82</v>
@@ -5349,13 +5349,13 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>64</v>
@@ -5364,7 +5364,7 @@
         <v>65</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>82</v>
@@ -5381,13 +5381,13 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>64</v>
@@ -5396,7 +5396,7 @@
         <v>65</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>82</v>
@@ -5413,13 +5413,13 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>64</v>
@@ -5428,7 +5428,7 @@
         <v>65</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>82</v>
@@ -5445,13 +5445,13 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>64</v>
@@ -5460,7 +5460,7 @@
         <v>65</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>82</v>
@@ -5477,13 +5477,13 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>64</v>
@@ -5492,7 +5492,7 @@
         <v>65</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>82</v>
@@ -5509,13 +5509,13 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>64</v>
@@ -5524,7 +5524,7 @@
         <v>65</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>82</v>
@@ -5541,13 +5541,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>64</v>
@@ -5556,7 +5556,7 @@
         <v>65</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>82</v>
@@ -5573,13 +5573,13 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>64</v>
@@ -5588,7 +5588,7 @@
         <v>65</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>82</v>
@@ -5605,13 +5605,13 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>64</v>
@@ -5620,7 +5620,7 @@
         <v>65</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>82</v>
@@ -5637,13 +5637,13 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>64</v>
@@ -5652,7 +5652,7 @@
         <v>65</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>82</v>
@@ -5669,13 +5669,13 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>64</v>
@@ -5684,7 +5684,7 @@
         <v>65</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>82</v>
@@ -5701,13 +5701,13 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>64</v>
@@ -5716,7 +5716,7 @@
         <v>65</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>82</v>
@@ -5733,13 +5733,13 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>64</v>
@@ -5748,7 +5748,7 @@
         <v>65</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>82</v>
@@ -5765,13 +5765,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>64</v>
@@ -5780,7 +5780,7 @@
         <v>65</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>82</v>
@@ -5797,13 +5797,13 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>64</v>
@@ -5812,7 +5812,7 @@
         <v>65</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>82</v>
@@ -5829,13 +5829,13 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>64</v>
@@ -5844,7 +5844,7 @@
         <v>65</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>82</v>
@@ -5861,13 +5861,13 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>64</v>
@@ -5876,7 +5876,7 @@
         <v>65</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>82</v>
@@ -5893,13 +5893,13 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>64</v>
@@ -5908,7 +5908,7 @@
         <v>65</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>82</v>
@@ -5925,13 +5925,13 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>64</v>
@@ -5940,7 +5940,7 @@
         <v>65</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>82</v>
@@ -5957,13 +5957,13 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>64</v>
@@ -5972,7 +5972,7 @@
         <v>65</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>82</v>
@@ -5989,13 +5989,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>64</v>
@@ -6004,7 +6004,7 @@
         <v>65</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>82</v>
@@ -6021,13 +6021,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>64</v>
@@ -6036,7 +6036,7 @@
         <v>65</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>82</v>
@@ -8012,7 +8012,7 @@
         <v>87</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>64</v>
@@ -8021,7 +8021,7 @@
         <v>65</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>82</v>
@@ -8044,7 +8044,7 @@
         <v>87</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>64</v>
@@ -8053,7 +8053,7 @@
         <v>65</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>82</v>
@@ -8076,7 +8076,7 @@
         <v>87</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>64</v>
@@ -8085,7 +8085,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>82</v>
@@ -8108,7 +8108,7 @@
         <v>87</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>64</v>
@@ -8117,7 +8117,7 @@
         <v>65</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>82</v>
@@ -8140,7 +8140,7 @@
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>64</v>
@@ -8149,7 +8149,7 @@
         <v>65</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>82</v>
@@ -8172,7 +8172,7 @@
         <v>87</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>64</v>
@@ -8181,7 +8181,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>82</v>
@@ -8204,7 +8204,7 @@
         <v>87</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>64</v>
@@ -8213,7 +8213,7 @@
         <v>65</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>82</v>
@@ -8236,7 +8236,7 @@
         <v>87</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>64</v>
@@ -8245,7 +8245,7 @@
         <v>65</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>82</v>
@@ -8268,7 +8268,7 @@
         <v>87</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>64</v>
@@ -8277,7 +8277,7 @@
         <v>65</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>82</v>
@@ -8300,7 +8300,7 @@
         <v>87</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>64</v>
@@ -8309,7 +8309,7 @@
         <v>65</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>82</v>
@@ -8332,7 +8332,7 @@
         <v>87</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>64</v>
@@ -8341,7 +8341,7 @@
         <v>65</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>82</v>
@@ -8364,7 +8364,7 @@
         <v>87</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>64</v>
@@ -8373,7 +8373,7 @@
         <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>82</v>
@@ -8396,7 +8396,7 @@
         <v>87</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>64</v>
@@ -8405,7 +8405,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>82</v>
@@ -8428,7 +8428,7 @@
         <v>87</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>64</v>
@@ -8437,7 +8437,7 @@
         <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>82</v>
@@ -8460,7 +8460,7 @@
         <v>87</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>64</v>
@@ -8469,7 +8469,7 @@
         <v>65</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>82</v>
@@ -8492,7 +8492,7 @@
         <v>87</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>64</v>
@@ -8501,7 +8501,7 @@
         <v>65</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>82</v>
@@ -8524,7 +8524,7 @@
         <v>87</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>64</v>
@@ -8533,7 +8533,7 @@
         <v>65</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>82</v>
@@ -8556,7 +8556,7 @@
         <v>87</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>64</v>
@@ -8565,7 +8565,7 @@
         <v>65</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>82</v>
@@ -8588,7 +8588,7 @@
         <v>87</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>64</v>
@@ -8597,7 +8597,7 @@
         <v>65</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>82</v>
@@ -8620,7 +8620,7 @@
         <v>87</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>64</v>
@@ -8629,7 +8629,7 @@
         <v>65</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>82</v>
@@ -8652,7 +8652,7 @@
         <v>87</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>64</v>
@@ -8661,7 +8661,7 @@
         <v>65</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>82</v>
@@ -8684,7 +8684,7 @@
         <v>87</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>64</v>
@@ -8693,7 +8693,7 @@
         <v>65</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>82</v>
@@ -8716,7 +8716,7 @@
         <v>87</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>64</v>
@@ -8725,7 +8725,7 @@
         <v>65</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>82</v>
@@ -8748,7 +8748,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>64</v>
@@ -8757,7 +8757,7 @@
         <v>65</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>82</v>
@@ -8780,7 +8780,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>64</v>
@@ -8789,7 +8789,7 @@
         <v>65</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>82</v>
@@ -8812,7 +8812,7 @@
         <v>87</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>64</v>
@@ -8821,7 +8821,7 @@
         <v>65</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>82</v>
@@ -8844,7 +8844,7 @@
         <v>87</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>64</v>
@@ -8853,7 +8853,7 @@
         <v>65</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>82</v>
@@ -8876,7 +8876,7 @@
         <v>87</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>64</v>
@@ -8885,7 +8885,7 @@
         <v>65</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>82</v>
@@ -8908,7 +8908,7 @@
         <v>87</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>64</v>
@@ -8917,7 +8917,7 @@
         <v>65</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>82</v>
@@ -8940,7 +8940,7 @@
         <v>87</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>64</v>
@@ -8949,7 +8949,7 @@
         <v>65</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>82</v>
@@ -8972,7 +8972,7 @@
         <v>87</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>64</v>
@@ -8981,7 +8981,7 @@
         <v>65</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>82</v>
@@ -9004,7 +9004,7 @@
         <v>87</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>64</v>
@@ -9013,7 +9013,7 @@
         <v>65</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>82</v>
@@ -9036,7 +9036,7 @@
         <v>87</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>64</v>
@@ -9045,7 +9045,7 @@
         <v>65</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>82</v>
@@ -9068,7 +9068,7 @@
         <v>87</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>64</v>
@@ -9077,7 +9077,7 @@
         <v>65</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>82</v>
@@ -9100,7 +9100,7 @@
         <v>87</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>64</v>
@@ -9109,7 +9109,7 @@
         <v>65</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>82</v>
@@ -9132,7 +9132,7 @@
         <v>87</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>64</v>
@@ -9141,7 +9141,7 @@
         <v>65</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>82</v>
@@ -9164,7 +9164,7 @@
         <v>87</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>64</v>
@@ -9173,7 +9173,7 @@
         <v>65</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>82</v>
@@ -9196,7 +9196,7 @@
         <v>87</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>64</v>
@@ -9205,7 +9205,7 @@
         <v>65</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>82</v>
@@ -9228,7 +9228,7 @@
         <v>87</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>64</v>
@@ -9237,7 +9237,7 @@
         <v>65</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>82</v>
@@ -9260,7 +9260,7 @@
         <v>87</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>64</v>
@@ -9269,7 +9269,7 @@
         <v>65</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>82</v>
@@ -9292,7 +9292,7 @@
         <v>87</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>64</v>
@@ -9301,7 +9301,7 @@
         <v>65</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>82</v>
@@ -9324,7 +9324,7 @@
         <v>87</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>64</v>
@@ -9333,7 +9333,7 @@
         <v>65</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>82</v>
@@ -9356,7 +9356,7 @@
         <v>87</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>64</v>
@@ -9365,7 +9365,7 @@
         <v>65</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>82</v>
@@ -9388,7 +9388,7 @@
         <v>87</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>64</v>
@@ -9397,7 +9397,7 @@
         <v>65</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>82</v>
@@ -9420,7 +9420,7 @@
         <v>87</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>64</v>
@@ -9429,7 +9429,7 @@
         <v>65</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>82</v>
@@ -9452,7 +9452,7 @@
         <v>87</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>64</v>
@@ -9461,7 +9461,7 @@
         <v>65</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>82</v>
@@ -9484,7 +9484,7 @@
         <v>87</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>64</v>
@@ -9493,7 +9493,7 @@
         <v>65</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>82</v>
@@ -9516,7 +9516,7 @@
         <v>87</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>64</v>
@@ -9525,7 +9525,7 @@
         <v>65</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>82</v>
@@ -9548,7 +9548,7 @@
         <v>87</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>64</v>
@@ -9557,7 +9557,7 @@
         <v>65</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>82</v>
